--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16922F02-0B09-44B6-BC48-8BC98DA4D68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19440" windowHeight="12570" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TOC" sheetId="1" r:id="rId1"/>
@@ -13,17 +12,26 @@
     <sheet name="Sanity" sheetId="11" r:id="rId3"/>
     <sheet name="Regression" sheetId="9" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -233,13 +241,157 @@
   </si>
   <si>
     <t>TC35</t>
+  </si>
+  <si>
+    <t>TC_update_order</t>
+  </si>
+  <si>
+    <t>Order Update Flag</t>
+  </si>
+  <si>
+    <t>TC_uploadFile_From_BannerOfIndexPage_PickUpCCFlow</t>
+  </si>
+  <si>
+    <t>TC_uploadFile_From_BannerOfIndexPage_PickUpFexAccFlow</t>
+  </si>
+  <si>
+    <t>TC_uploadFile_From_BannerOfIndexPage_Shipping_GroundUS_CCFlow</t>
+  </si>
+  <si>
+    <t>TC_uploadFile_From_BannerOfIndexPage_Shipping_FedEx_Priority_Overnight_FedAccFlow</t>
+  </si>
+  <si>
+    <t>TC_FedEx_ShippingAcc_Accflow</t>
+  </si>
+  <si>
+    <t>TC_FedEx_ShippingAcc_CCflow</t>
+  </si>
+  <si>
+    <t>TC_NDC_Acc_Flow</t>
+  </si>
+  <si>
+    <t>TC_Canvaflow</t>
+  </si>
+  <si>
+    <t>PickUpflowUsingCCPay_viaLogin</t>
+  </si>
+  <si>
+    <t>PickUpflowUsingFedExAcc_viaLogin</t>
+  </si>
+  <si>
+    <t>ShippingFLowUsingCCPay_viaLogin</t>
+  </si>
+  <si>
+    <t>ShippingFLowUsingFedExPay_viaLogin</t>
+  </si>
+  <si>
+    <t>TC_BusinessCards_Preminum_flow_CC</t>
+  </si>
+  <si>
+    <t>TC_BusinessCards_Preminum_flow_FedExAcc</t>
+  </si>
+  <si>
+    <t>Business Cards - Premium</t>
+  </si>
+  <si>
+    <t>TC_PPT_flow_CC</t>
+  </si>
+  <si>
+    <t>Presentations</t>
+  </si>
+  <si>
+    <t>TC_PPT_flow_FedExAcc</t>
+  </si>
+  <si>
+    <t>Outdoor Banners</t>
+  </si>
+  <si>
+    <t>TC_Outdoor_Banners_PickUp_CC</t>
+  </si>
+  <si>
+    <t>TC_Outdoor_Banners_PickUp_FedexAcc</t>
+  </si>
+  <si>
+    <t>TC_Outdoor_Banners_Shipping_CC</t>
+  </si>
+  <si>
+    <t>TC_Outdoor_Banners_Shipping_FedexAcc</t>
+  </si>
+  <si>
+    <t>TC_checkoutUsing_MiniCart_Pickup_CC</t>
+  </si>
+  <si>
+    <t>Resumes</t>
+  </si>
+  <si>
+    <t>TC_checkoutUsing_MiniCart_Shipping_FedexAcc</t>
+  </si>
+  <si>
+    <t>Manuals</t>
+  </si>
+  <si>
+    <t>TC_editMiniCart_Quantity_PickUp_CC</t>
+  </si>
+  <si>
+    <t>TC_Delete_All_itemsFromMiniCart</t>
+  </si>
+  <si>
+    <t>TC_BusinessCards_QuickLinks_pickUP_CCFlow</t>
+  </si>
+  <si>
+    <t>Business Cards</t>
+  </si>
+  <si>
+    <t>TC_BusinessCards_QuickLinks_Shipping_FedExAccFlow</t>
+  </si>
+  <si>
+    <t>TC_BusinessCardsPreminum_QuickLinks_Flow</t>
+  </si>
+  <si>
+    <t>TC_NoteCards_QuickLinks_pickUP_CCFlow</t>
+  </si>
+  <si>
+    <t>Note Cards</t>
+  </si>
+  <si>
+    <t>TC_NoteCards_QuickLinks_Shipping_FedExAccFlow</t>
+  </si>
+  <si>
+    <t>TC_NoteCardsPreminum_QuickLinks_Flow</t>
+  </si>
+  <si>
+    <t>TC_ChangePickupToShipping_CCFlow</t>
+  </si>
+  <si>
+    <t>TC_ChangePickupToShipping_FedExAccFlow</t>
+  </si>
+  <si>
+    <t>TC_ChangeShippingToPickup_CCFlow</t>
+  </si>
+  <si>
+    <t>TC_ChangeShippingToPickup_FedExAccFlow</t>
+  </si>
+  <si>
+    <t>TC_loginAtCheckoutScreen_Shipping_CCFlow</t>
+  </si>
+  <si>
+    <t>TC_loginAtCheckoutScreen_Shipping_FedExAccFlow</t>
+  </si>
+  <si>
+    <t>TC_loginAtCheckoutScreen_Pickup_CCFlow</t>
+  </si>
+  <si>
+    <t>TC_loginAtCheckoutScreen_Pickup_FedExAccFlow</t>
+  </si>
+  <si>
+    <t>TC_TaxExemptedAccFlow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -385,6 +537,12 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,7 +603,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -480,7 +638,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -657,22 +815,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -683,7 +841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -694,7 +852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -712,20 +870,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC95BAF-5F92-4570-BA5D-CCB9747789C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="45">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -762,7 +920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -788,7 +946,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -811,7 +969,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -837,7 +995,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -867,19 +1025,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499DE41-16E7-4559-B87D-A2EC627B7AB0}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I72"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="40.28515625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="26.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="63" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -889,13 +1050,14 @@
       <c r="C1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="12"/>
+      <c r="D1" s="11"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -906,22 +1068,25 @@
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I2" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -931,23 +1096,26 @@
       <c r="C3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -957,21 +1125,24 @@
       <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H4" s="12"/>
+      <c r="I4" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30">
       <c r="A5" s="14">
         <v>3</v>
       </c>
@@ -981,23 +1152,26 @@
       <c r="C5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>16</v>
+      <c r="F5" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I5" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30">
       <c r="A6" s="14">
         <v>4</v>
       </c>
@@ -1007,21 +1181,24 @@
       <c r="C6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -1031,23 +1208,26 @@
       <c r="C7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>16</v>
+      <c r="F7" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I7" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="30">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -1057,23 +1237,26 @@
       <c r="C8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>16</v>
+      <c r="F8" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I8" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="30">
       <c r="A9" s="14">
         <v>7</v>
       </c>
@@ -1083,23 +1266,26 @@
       <c r="C9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>16</v>
+      <c r="F9" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G9" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I9" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30">
       <c r="A10" s="14">
         <v>8</v>
       </c>
@@ -1109,23 +1295,26 @@
       <c r="C10" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>16</v>
+      <c r="F10" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I10" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30">
       <c r="A11" s="14">
         <v>9</v>
       </c>
@@ -1135,23 +1324,26 @@
       <c r="C11" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>16</v>
+      <c r="F11" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I11" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30">
       <c r="A12" s="14">
         <v>10</v>
       </c>
@@ -1161,23 +1353,26 @@
       <c r="C12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="F12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="G12" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="14">
         <v>11</v>
       </c>
@@ -1187,21 +1382,24 @@
       <c r="C13" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="F13" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H13" s="12"/>
+      <c r="I13" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30">
       <c r="A14" s="14">
         <v>12</v>
       </c>
@@ -1211,23 +1409,26 @@
       <c r="C14" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>16</v>
+      <c r="F14" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I14" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="30">
       <c r="A15" s="14">
         <v>13</v>
       </c>
@@ -1237,21 +1438,24 @@
       <c r="C15" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="G15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="30">
       <c r="A16" s="14">
         <v>14</v>
       </c>
@@ -1261,23 +1465,26 @@
       <c r="C16" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>16</v>
+      <c r="F16" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I16" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30">
       <c r="A17" s="14">
         <v>15</v>
       </c>
@@ -1287,23 +1494,26 @@
       <c r="C17" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>16</v>
+      <c r="F17" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I17" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="30">
       <c r="A18" s="14">
         <v>16</v>
       </c>
@@ -1313,23 +1523,26 @@
       <c r="C18" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>16</v>
+      <c r="F18" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I18" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30">
       <c r="A19" s="14">
         <v>17</v>
       </c>
@@ -1339,23 +1552,26 @@
       <c r="C19" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>16</v>
+      <c r="F19" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I19" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="30">
       <c r="A20" s="14">
         <v>18</v>
       </c>
@@ -1365,23 +1581,26 @@
       <c r="C20" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>16</v>
+      <c r="F20" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I20" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30">
       <c r="A21" s="14">
         <v>19</v>
       </c>
@@ -1391,23 +1610,26 @@
       <c r="C21" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="F21" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="G21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="14">
         <v>20</v>
       </c>
@@ -1417,21 +1639,24 @@
       <c r="C22" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="F22" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="G22" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H22" s="12"/>
+      <c r="I22" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="30">
       <c r="A23" s="14">
         <v>21</v>
       </c>
@@ -1441,23 +1666,26 @@
       <c r="C23" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>16</v>
+      <c r="F23" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I23" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30">
       <c r="A24" s="14">
         <v>22</v>
       </c>
@@ -1467,21 +1695,24 @@
       <c r="C24" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="F24" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H24" s="12"/>
+      <c r="I24" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30">
       <c r="A25" s="14">
         <v>23</v>
       </c>
@@ -1491,23 +1722,26 @@
       <c r="C25" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>16</v>
+      <c r="F25" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G25" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I25" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="30">
       <c r="A26" s="14">
         <v>24</v>
       </c>
@@ -1517,23 +1751,26 @@
       <c r="C26" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>16</v>
+      <c r="F26" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G26" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I26" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="30">
       <c r="A27" s="14">
         <v>25</v>
       </c>
@@ -1543,23 +1780,26 @@
       <c r="C27" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>16</v>
+      <c r="F27" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G27" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I27" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="30">
       <c r="A28" s="14">
         <v>26</v>
       </c>
@@ -1569,23 +1809,26 @@
       <c r="C28" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>16</v>
+      <c r="F28" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G28" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I28" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30">
       <c r="A29" s="14">
         <v>27</v>
       </c>
@@ -1595,23 +1838,26 @@
       <c r="C29" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>16</v>
+      <c r="F29" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I29" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="30">
       <c r="A30" s="14">
         <v>28</v>
       </c>
@@ -1621,23 +1867,26 @@
       <c r="C30" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="F30" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="G30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H30" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="14">
         <v>29</v>
       </c>
@@ -1647,21 +1896,24 @@
       <c r="C31" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="F31" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="G31" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H31" s="12"/>
+      <c r="I31" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30">
       <c r="A32" s="14">
         <v>30</v>
       </c>
@@ -1671,19 +1923,1091 @@
       <c r="C32" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>16</v>
+      <c r="F32" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G32" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="I32" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="15">
+        <v>31</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30">
+      <c r="A34" s="15">
+        <v>32</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="30">
+      <c r="A35" s="15">
+        <v>33</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="5">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="5">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="5">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="5">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="5">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="5">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="18" customFormat="1">
+      <c r="A42" s="18">
+        <v>40</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="18" customFormat="1">
+      <c r="A43" s="18">
+        <v>41</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="18" customFormat="1">
+      <c r="A44" s="18">
+        <v>42</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="18" customFormat="1">
+      <c r="A45" s="18">
+        <v>43</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="5">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="5">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="5">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="5">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="5">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="5">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="5">
+        <v>50</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="5">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="5">
+        <v>52</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="5">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="5">
+        <v>54</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="5">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="5">
+        <v>56</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="5">
+        <v>57</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="5">
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="5">
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" s="17"/>
+      <c r="I61" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="5">
+        <v>60</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="5">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="5">
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="5">
+        <v>63</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H65" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="5">
+        <v>64</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="5">
+        <v>65</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="30">
+      <c r="A68" s="5">
+        <v>66</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="30">
+      <c r="A69" s="5">
+        <v>67</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="30">
+      <c r="A70" s="5">
+        <v>68</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="30">
+      <c r="A71" s="5">
+        <v>69</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="5">
+        <v>70</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1695,16 +3019,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EF23A6-AE7B-460A-91F2-06748D844505}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="45">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1715,7 +3039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1726,7 +3050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1737,7 +3061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1748,7 +3072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>3</v>
       </c>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7626CE21-6C82-424A-9031-6BEAE273BCC0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19440" windowHeight="12570" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TOC" sheetId="1" r:id="rId1"/>
@@ -12,9 +13,9 @@
     <sheet name="Sanity" sheetId="11" r:id="rId3"/>
     <sheet name="Regression" sheetId="9" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="126">
   <si>
     <t>ID</t>
   </si>
@@ -385,13 +386,37 @@
   </si>
   <si>
     <t>TC_TaxExemptedAccFlow</t>
+  </si>
+  <si>
+    <t>TC_PromoCode_PickUp_CC_Flow</t>
+  </si>
+  <si>
+    <t>TC_PromoCode_UpdateDefaulttqy_Shiping_FedExAcc_Flow</t>
+  </si>
+  <si>
+    <t>Corrugated Plastic Sign</t>
+  </si>
+  <si>
+    <t>TC_Corrugated_plastic_sign_Pickup_CCflow</t>
+  </si>
+  <si>
+    <t>TC_Metal_Sign_Pickup_Ccflow</t>
+  </si>
+  <si>
+    <t>Metal Sign</t>
+  </si>
+  <si>
+    <t>TC_Yard_Sign_Pickup_FedExACCflow</t>
+  </si>
+  <si>
+    <t>Yard Sign</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -542,7 +567,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,7 +627,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -638,7 +662,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -815,22 +839,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -841,7 +865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -852,7 +876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -870,20 +894,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC95BAF-5F92-4570-BA5D-CCB9747789C4}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="3" max="3" width="28.90625" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.90625" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45">
+    <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -894,7 +918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -920,7 +944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -946,7 +970,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -969,7 +993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -995,7 +1019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1025,22 +1049,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I72"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499DE41-16E7-4559-B87D-A2EC627B7AB0}">
+  <dimension ref="A1:I77"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="5"/>
-    <col min="2" max="2" width="40.28515625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="26.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="8.90625" style="5"/>
+    <col min="2" max="2" width="40.36328125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="26.36328125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="20.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="63" customHeight="1">
+    <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -1057,7 +1081,7 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -1086,7 +1110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30">
+    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -1115,7 +1139,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -1142,7 +1166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>3</v>
       </c>
@@ -1171,7 +1195,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30">
+    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>4</v>
       </c>
@@ -1198,7 +1222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -1227,7 +1251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -1256,7 +1280,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>7</v>
       </c>
@@ -1285,7 +1309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>8</v>
       </c>
@@ -1314,7 +1338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="30">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>9</v>
       </c>
@@ -1343,7 +1367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30">
+    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>10</v>
       </c>
@@ -1372,7 +1396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>11</v>
       </c>
@@ -1399,7 +1423,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>12</v>
       </c>
@@ -1428,7 +1452,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="30">
+    <row r="15" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>13</v>
       </c>
@@ -1455,7 +1479,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>14</v>
       </c>
@@ -1484,7 +1508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="30">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>15</v>
       </c>
@@ -1513,7 +1537,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>16</v>
       </c>
@@ -1542,7 +1566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>17</v>
       </c>
@@ -1571,7 +1595,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>18</v>
       </c>
@@ -1600,7 +1624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30">
+    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>19</v>
       </c>
@@ -1629,7 +1653,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>20</v>
       </c>
@@ -1656,7 +1680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>21</v>
       </c>
@@ -1685,7 +1709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30">
+    <row r="24" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>22</v>
       </c>
@@ -1712,7 +1736,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>23</v>
       </c>
@@ -1741,7 +1765,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="30">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>24</v>
       </c>
@@ -1770,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>25</v>
       </c>
@@ -1799,7 +1823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>26</v>
       </c>
@@ -1828,7 +1852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="30">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="14">
         <v>27</v>
       </c>
@@ -1857,7 +1881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30">
+    <row r="30" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="14">
         <v>28</v>
       </c>
@@ -1886,7 +1910,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="14">
         <v>29</v>
       </c>
@@ -1913,7 +1937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="14">
         <v>30</v>
       </c>
@@ -1942,7 +1966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="15">
         <v>31</v>
       </c>
@@ -1971,7 +1995,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30">
+    <row r="34" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="15">
         <v>32</v>
       </c>
@@ -1997,7 +2021,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="15">
         <v>33</v>
       </c>
@@ -2023,7 +2047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>34</v>
       </c>
@@ -2052,7 +2076,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>35</v>
       </c>
@@ -2081,7 +2105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>36</v>
       </c>
@@ -2110,7 +2134,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>37</v>
       </c>
@@ -2139,7 +2163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>38</v>
       </c>
@@ -2168,7 +2192,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>39</v>
       </c>
@@ -2197,7 +2221,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="18" customFormat="1">
+    <row r="42" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18">
         <v>40</v>
       </c>
@@ -2223,7 +2247,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="18" customFormat="1">
+    <row r="43" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18">
         <v>41</v>
       </c>
@@ -2249,7 +2273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="18" customFormat="1">
+    <row r="44" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18">
         <v>42</v>
       </c>
@@ -2278,7 +2302,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="18" customFormat="1">
+    <row r="45" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="18">
         <v>43</v>
       </c>
@@ -2307,7 +2331,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>44</v>
       </c>
@@ -2336,7 +2360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>45</v>
       </c>
@@ -2365,7 +2389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>46</v>
       </c>
@@ -2391,7 +2415,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>47</v>
       </c>
@@ -2417,7 +2441,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>48</v>
       </c>
@@ -2440,7 +2464,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>49</v>
       </c>
@@ -2463,7 +2487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>50</v>
       </c>
@@ -2489,7 +2513,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>51</v>
       </c>
@@ -2515,7 +2539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>52</v>
       </c>
@@ -2538,7 +2562,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>53</v>
       </c>
@@ -2564,7 +2588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>54</v>
       </c>
@@ -2587,7 +2611,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>55</v>
       </c>
@@ -2610,7 +2634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>56</v>
       </c>
@@ -2633,7 +2657,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>57</v>
       </c>
@@ -2659,7 +2683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>58</v>
       </c>
@@ -2685,7 +2709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>59</v>
       </c>
@@ -2709,7 +2733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>60</v>
       </c>
@@ -2735,7 +2759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>61</v>
       </c>
@@ -2761,7 +2785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>62</v>
       </c>
@@ -2777,10 +2801,10 @@
       <c r="E64" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F64" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="17" t="s">
+      <c r="F64" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="12" t="s">
         <v>17</v>
       </c>
       <c r="H64" s="5" t="s">
@@ -2790,7 +2814,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>63</v>
       </c>
@@ -2806,20 +2830,20 @@
       <c r="E65" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F65" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="17" t="s">
+      <c r="F65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H65" s="17" t="s">
+      <c r="H65" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>64</v>
       </c>
@@ -2835,7 +2859,7 @@
       <c r="E66" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F66" s="21" t="s">
+      <c r="F66" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G66" s="5" t="s">
@@ -2845,7 +2869,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>65</v>
       </c>
@@ -2861,18 +2885,18 @@
       <c r="E67" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="F67" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="17"/>
+      <c r="H67" s="12"/>
       <c r="I67" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="30">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>66</v>
       </c>
@@ -2888,20 +2912,20 @@
       <c r="E68" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H68" s="17" t="s">
+      <c r="F68" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I68" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="30">
+      <c r="I68" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>67</v>
       </c>
@@ -2917,20 +2941,20 @@
       <c r="E69" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H69" s="17" t="s">
+      <c r="F69" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" s="12" t="s">
         <v>47</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>68</v>
       </c>
@@ -2946,18 +2970,18 @@
       <c r="E70" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F70" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" s="17" t="s">
+      <c r="F70" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="30">
+      <c r="H70" s="12"/>
+      <c r="I70" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>69</v>
       </c>
@@ -2973,18 +2997,18 @@
       <c r="E71" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F71" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G71" s="17" t="s">
+      <c r="F71" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H71" s="17"/>
+      <c r="H71" s="12"/>
       <c r="I71" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>70</v>
       </c>
@@ -3000,14 +3024,150 @@
       <c r="E72" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="F72" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="17"/>
+      <c r="H72" s="12"/>
       <c r="I72" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="5">
+        <v>71</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="5">
+        <v>72</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="5">
+        <v>73</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="5">
+        <v>74</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" s="5">
+        <v>75</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I77" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3019,16 +3179,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EF23A6-AE7B-460A-91F2-06748D844505}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="45">
+    <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3039,7 +3199,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -3050,7 +3210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -3061,7 +3221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -3072,7 +3232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>3</v>
       </c>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7626CE21-6C82-424A-9031-6BEAE273BCC0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07539AA-02CC-4A41-9E85-D2DF191DDCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TOC" sheetId="1" r:id="rId1"/>
@@ -848,13 +848,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.36328125" customWidth="1"/>
-    <col min="3" max="3" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -865,7 +865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -896,18 +896,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC95BAF-5F92-4570-BA5D-CCB9747789C4}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="28.90625" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="13.90625" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -918,7 +918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -944,7 +944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -970,7 +970,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -993,7 +993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1051,20 +1051,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499DE41-16E7-4559-B87D-A2EC627B7AB0}">
   <dimension ref="A1:I77"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="5"/>
-    <col min="2" max="2" width="40.36328125" style="5" customWidth="1"/>
-    <col min="3" max="4" width="26.36328125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="20.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="5"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="40.33203125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="26.33203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -1081,7 +1081,7 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>3</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>25</v>
@@ -1195,7 +1195,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>4</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>7</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>8</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>9</v>
       </c>
@@ -1351,8 +1351,8 @@
       <c r="D11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>23</v>
+      <c r="E11" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>25</v>
@@ -1367,7 +1367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>10</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>11</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>12</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>25</v>
@@ -1452,7 +1452,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>13</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>14</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>15</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>16</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>17</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>18</v>
       </c>
@@ -1608,8 +1608,8 @@
       <c r="D20" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>23</v>
+      <c r="E20" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>25</v>
@@ -1624,7 +1624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>19</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>20</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>21</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>25</v>
@@ -1709,7 +1709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>22</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>23</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>24</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>25</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>26</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
         <v>27</v>
       </c>
@@ -1865,8 +1865,8 @@
       <c r="D29" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>23</v>
+      <c r="E29" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>25</v>
@@ -1881,7 +1881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
         <v>28</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
         <v>29</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
         <v>30</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>25</v>
@@ -1966,7 +1966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
         <v>31</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="15">
         <v>32</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="15">
         <v>33</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>34</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>35</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>36</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>37</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>38</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>39</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="18">
         <v>40</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="18">
         <v>41</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="18">
         <v>42</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>43</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>44</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>46</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>47</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>48</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>49</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>50</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>51</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>52</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>53</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>54</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>55</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>56</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>57</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>58</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>59</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>60</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>61</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>62</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>63</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>64</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>65</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>66</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>67</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>68</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>69</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>70</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>71</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>72</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>73</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>74</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>75</v>
       </c>
@@ -3181,14 +3181,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EF23A6-AE7B-460A-91F2-06748D844505}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07539AA-02CC-4A41-9E85-D2DF191DDCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43E58B6-AE6C-4FA5-9294-3E82137D6CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="132">
   <si>
     <t>ID</t>
   </si>
@@ -410,6 +410,24 @@
   </si>
   <si>
     <t>Yard Sign</t>
+  </si>
+  <si>
+    <t>TC_PostCards_update_Product_Print_properties_Size</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_AllSize</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_StdWhitePaper</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_ProWhitePaper</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_CardStocksSpecialty</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_StdColorPaper</t>
   </si>
 </sst>
 </file>
@@ -1050,11 +1068,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499DE41-16E7-4559-B87D-A2EC627B7AB0}">
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
-    <col min="2" max="2" width="40.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="51.109375" style="5" customWidth="1"/>
     <col min="3" max="4" width="26.33203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="20.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.77734375" style="5" bestFit="1" customWidth="1"/>
@@ -3169,6 +3187,156 @@
       </c>
       <c r="I77" s="5" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="5">
+        <v>76</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="5">
+        <v>77</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="5">
+        <v>78</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="5">
+        <v>79</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="5">
+        <v>80</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="5">
+        <v>81</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43E58B6-AE6C-4FA5-9294-3E82137D6CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C67771-4861-416C-BB37-9248A02DDF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="137">
   <si>
     <t>ID</t>
   </si>
@@ -428,6 +428,21 @@
   </si>
   <si>
     <t>TC_Manuals_update_Product_Print_properties_StdColorPaper</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_ProColorPaper</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_Color_BlackWhite</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_Sides</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_Orientation</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_BindingandFinishing_Binding</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499DE41-16E7-4559-B87D-A2EC627B7AB0}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -3337,6 +3352,130 @@
       </c>
       <c r="I83" s="5" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="5">
+        <v>82</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="5">
+        <v>83</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
+        <v>84</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
+        <v>85</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" s="5">
+        <v>86</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C67771-4861-416C-BB37-9248A02DDF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2A74A3-3640-4E83-BC4A-32A25AAB273D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="140">
   <si>
     <t>ID</t>
   </si>
@@ -443,6 +443,15 @@
   </si>
   <si>
     <t>TC_Manuals_update_Product_Print_properties_BindingandFinishing_Binding</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_BindingandFinishing_Cutting</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_BindingandFinishing_Lamination</t>
+  </si>
+  <si>
+    <t>TC_Manuals_update_Product_Print_properties_AdvOptions_BlankSheets</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3499DE41-16E7-4559-B87D-A2EC627B7AB0}">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -3475,6 +3484,78 @@
         <v>40</v>
       </c>
       <c r="I88" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="5">
+        <v>87</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" s="5">
+        <v>88</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="5">
+        <v>89</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>30</v>
       </c>
     </row>

--- a/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
+++ b/src/main/java/com/NonKeyword_FutureReadyFramework/automation/data/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2A74A3-3640-4E83-BC4A-32A25AAB273D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0101A567-2682-42B1-8095-FE53E6DF6150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1888,7 +1888,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>29</v>
@@ -2549,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>29</v>
@@ -3285,7 +3285,7 @@
         <v>16</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>30</v>
@@ -3383,7 +3383,7 @@
         <v>16</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>30</v>
